--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.75776247942628</v>
+        <v>5.48563640290677</v>
       </c>
       <c r="D2" t="n">
-        <v>75.77437193634761</v>
+        <v>12.31333543965649</v>
       </c>
       <c r="E2" t="n">
-        <v>18.53524249989996</v>
+        <v>3.011976906233743</v>
       </c>
       <c r="F2" t="n">
-        <v>7.019981424725697</v>
+        <v>1.140746981517926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.08771243788932</v>
+        <v>6.676753271157015</v>
       </c>
       <c r="D3" t="n">
-        <v>76.50214857509175</v>
+        <v>12.43159914345241</v>
       </c>
       <c r="E3" t="n">
-        <v>18.53524249989996</v>
+        <v>3.011976906233743</v>
       </c>
       <c r="F3" t="n">
-        <v>7.019981424725697</v>
+        <v>1.140746981517926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>76.22611798909948</v>
+        <v>12.38674417322867</v>
       </c>
       <c r="D4" t="n">
-        <v>91.01654585214496</v>
+        <v>14.79018870097356</v>
       </c>
       <c r="E4" t="n">
-        <v>18.53524249989996</v>
+        <v>3.011976906233743</v>
       </c>
       <c r="F4" t="n">
-        <v>7.019981424725697</v>
+        <v>1.140746981517926</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
